--- a/reports/2026/07/Sugar News 2026-07-21.xlsx
+++ b/reports/2026/07/Sugar News 2026-07-21.xlsx
@@ -70,7 +70,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -83,6 +83,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -481,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="55" customWidth="1" style="2" min="2" max="2"/>
@@ -505,397 +508,285 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="180" customHeight="1" s="2">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="2" ht="60" customHeight="1" s="2">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>巴西</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 UkrAgroConsult报道：US tariffs could hit Brazil’s sugar and ethanol producers hard。来源：UkrAgroConsult（https://news.google.com/rss/articles/CBMingFBVV95cUxQeVc3VE1wc3lIOEQ4d09NakR2UTZxZk9KS1JfM2d5Q3R1dnJHLTJ0U3F1MmRRQ251QkdBZmNSRE5XZHhmd2hyM1p0Y2RkcGNmZXRRdTlDcEplY3ctUHVfMTJ1TzNRTElKYnB5TGNVdmE3RlRVY0dTWklROWRlNTEzNk0wbkdmQUtkS1VSNTBBdy0xY0RZS1BSMWtXaFVLZw?oc=5）</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>偏多糖价：乙醇需求或政策推进可能增加糖料制醇吸引力，减少部分制糖供应。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="180" customHeight="1" s="2">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>美国关税可能抬高巴西糖和乙醇生产商的出口成本，并增加贸易流向调整压力。巴西是全球主要食糖出口国，若关税影响出口利润或物流安排，短期会提高国际糖源供应的不确定性。来源：UkrAgroConsult（https://news.google.com/rss/articles/CBMingFBVV95cUxQeVc3VE1wc3lIOEQ4d09NakR2UTZxZk9KS1JfM2d5Q3R1dnJHLTJ0U3F1MmRRQ251QkdBZmNSRE5XZHhmd2hyM1p0Y2RkcGNmZXRRdTlDcEplY3ctUHVfMTJ1TzNRTElKYnB5TGNVdmE3RlRVY0dTWklROWRlNTEzNk0wbkdmQUtkS1VSNTBBdy0xY0RZS1BSMWtXaFVLZw?oc=5）</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>利多：关税扰动可能削弱巴西糖醇出口竞争力并影响可供出口糖源，对国际糖价形成风险支撑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1" s="2">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>巴西</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 EIN News报道：Organic Molasses Market Poised for Strong Growth as Demand for Natural Sweeteners and Sustainable Feed Solutions。来源：EIN News（https://news.google.com/rss/articles/CBMi6gFBVV95cUxOQTFzN3lmeUxxejZjN3BZR2V5OFNZOFgzTS0xSjJIRlByMmc0VmpILWtUZzhLRzRkTWlOcnZXSXpXYUpXTGl1clhCeVBqaEx6ZmxLSENUUndZY2ZOQ3hGT0VRRllpUmgtdWM0RDJBb2JQaHJSeVJYSXViNFJtMHEyWld4VkNKQU9KcGNLUFlYU2JFa3RYbHlhbU9IVk1aR3RKMnZVVFFyTTB3VHFiVmFmY3Z2SDFXRllTR2xURGtYOXU2NXVFWWRUY3hxWE1qVlR5eE5pM2kyTWtiSlhkN09sMlB4RC1MNWZpTmc?oc=5）</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="180" customHeight="1" s="2">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>巴西</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 ChiniMandi报道：Adecoagro acquires Caarapó sugar and ethanol mill in Brazil。来源：ChiniMandi（https://news.google.com/rss/articles/CBMikAFBVV95cUxPZkUtbV9IUkhSUS1YbjgwQXhQbUlNclhhQ0IzU3p1eGZpNm1KMlJFZ2t2RVpJc3MzempTVC0wbHlsTjB4eFkzUjU0aUFrc3QtUURxQmh4ZW0yV2N0RGNvUENCOHpOak9xWUdBLTFtSmtIU3BoN0dCOGlkX3g2V1JGSDcyUWMzci1KSVo5TVRJUE8?oc=5）</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>偏多糖价：乙醇需求或政策推进可能增加糖料制醇吸引力，减少部分制糖供应。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="180" customHeight="1" s="2">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>巴西</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 BioEnergy Times报道：Indonesia targets E10 ethanol-blended petrol in 2027, plans gradual shift to E20。来源：BioEnergy Times（https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWXJoODE4aVNhaklPblhDTEpyQ2NnX3ZTaFEtZGVnMDNVWDlIcTlMSW5Xc3VDelpIZHUxRmdpaHhWRkh2VDRRa3plQm40Q2xDanc1OUZBczBibXdjTXBHM2VXb0M3WV9wYlN5dGo4UEc0TnBuRTI4cGhWTmlTRXZIMjhaQUJZendmemZrUjd4R215dGpIYzhkamNCbUpnOFBxcnRnRVBFcHJEdWs?oc=5）</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>偏多糖价：乙醇需求或政策推进可能增加糖料制醇吸引力，减少部分制糖供应。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="180" customHeight="1" s="2">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>巴西</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 FBC News报道：Ministry lacks supermarket sugar tracking system。来源：FBC News（https://news.google.com/rss/articles/CBMiiAFBVV95cUxQWkVlOE1PYU9RdWtDNVNfcS1jNGxSLXhoUGhmSks5eVkxOEE4TmZJUVA5WG90MXZQZDBySlQyeXhXb0FjcmdHb1F3ZklHVFZxYkFPYXlmZlhKTHdYWU1JZFdOaEpjWm03VmRqTXZRcEMwVjRTZ25LOEZ1SlVGWENjMUVmd2hHVEdi?oc=5）</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="180" customHeight="1" s="2">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>印度</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 Press Trust of India报道：Lokshakti Sugar Advances High-Efficiency Sugar Manufacturing with Multi-Equipment Order to SED。来源：Press Trust of India（https://news.google.com/rss/articles/CBMi1wFBVV95cUxONDRJa1ltOXFoOUtlR2xNSktVTTBLcDRyeHl1ekZxSW9BYUU3RHJtalhXODRnMWZlUU84N2xabGZXVm9JQXgxYU11U0R1QmlSbnZFdkNPbThFbl96TFg0QUlFOUlWUkpuaGxtTl8yMlNOdVFSQk1QRDlENDNiZmpzWDBCZE9QaGtlYU95MmgtejY5OEJJLUVXelpsTEwxcmZNaVFwbTNRcDhJdDN6aHpVM1FwTVgydjZkeUw5M0tROTlkMnFpU2VyZzdkZjkybUd1cEdMVllwMA?oc=5）</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="180" customHeight="1" s="2">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>印度</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 ChiniMandi报道：UP leads India in sugar, sugarcane and ethanol production: Yogi Adityanath。来源：ChiniMandi（https://news.google.com/rss/articles/CBMiogFBVV95cUxPV1FkN0RRWV92Q09yU2dEUUZfSC1PcThidlZuSENFVmVfM2k0YjlyNjYtVW44S0pfM19pdEFXTTBiS1dJcVpsMDZLcWlETlZuTjNVMGFNTElreE1MaVNaandoeGUwNkJ1d2JBbFV0M1ZXc2JOWjlJU3YtNlZsZFdwZ1lVUXVzVmlwcXVkc3JtYjRPeVV6eHZWclllSE9iRmkwWkE?oc=5）</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>偏多糖价：乙醇需求或政策推进可能增加糖料制醇吸引力，减少部分制糖供应。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="180" customHeight="1" s="2">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>印度</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 ChiniMandi报道：Sugarcane cultivation in Andhra faces fresh setback amid El Niño fears。来源：ChiniMandi（https://news.google.com/rss/articles/CBMinwFBVV95cUxQcGJRWWttWDRyUHJuNDJ5dTRlNkpLZEg2MUFOSDlGczhRY19lWlpWTDZTdWFPcERjdFhmbU5QNEdzQlk4T1ZUUmZTLW5RSjdjeDRVeVV5Wk9ocXI3V1Q3WjBITE90eEN0RlBnOHF5TFQ2SVdNZW0zanBnZ2JuSXc1VzJzYWVOXzd2S2xFUDFMYmdJUXdyNGoyUnNWZURNbVE?oc=5）</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="180" customHeight="1" s="2">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>印度</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 ChiniMandi报道：Belagavi set to strengthen dominance in Karnataka's sugar sector with 13 new mill proposals。来源：ChiniMandi（https://news.google.com/rss/articles/CBMiugFBVV95cUxQclpwbzdmeE1MUVJmNXZjUlVRbEtmS0hjeGlJVTZhN3JlZWRRNlVYLTVCamk3MDM1Q2xkQ0o3VlVIdVlBWFFKOHluLTRwdmxDU0RxNl9vdnotMURiTWNkYWxaY2N6VHljS3JDcm1pckp5Y2ZqZS1teXo4YmxySTEzSlU3OXdBbU1FakswUUtDODJJODEtN0tKTjBESnlmaW5ac2JWaWRpUENOMTVuUUdmbWFqeFMzMjY1OUE?oc=5）</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="180" customHeight="1" s="2">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>印度</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 Siliconindia报道：Sugar Trade Body Calls Shortage Fears 'Unwarranted', Urges Steady Supply。来源：Siliconindia（https://news.google.com/rss/articles/CBMizgFBVV95cUxNbVFIbmZQTnZwbGdUdHdkck13M1Y2OF9yR0JqU2g5TmJKTXFta3dyX0JSS1NRSmh6dzlSX2FjbExqWFVBZnRlMjRlOXVzaHdjbDhXbFpVYVRrT0hFTXVIMUYzcV8tNXpXYkszUmRqZDFjUGxmZF9WR1VraU5nMW9Vc21Gdy16cWpLaVY1VTlMdlUwcjlOc29BU3MyNlZtMWRFVllBc0JJR0NBTTlQd1JEX1ZoMUczTlFDQW55UEY2YnJxbXhOMUI5dnlPa0pBdw?oc=5）</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>偏多糖价：贸易限制或供应扰动可能减少国际市场可用糖源。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="180" customHeight="1" s="2">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>印度</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 The Times of India报道：Wangchuk continues to refuse IV fluids despite medical advice; low blood sugar, potassium persist。来源：The Times of India（https://news.google.com/rss/articles/CBMi9gFBVV95cUxNSzl3TzZQN3lQZ01DNkQxN21ObFlvc2JXa1dQa2RpYjB2NlJfekU5WmRWNHpBdVlZbEt2Z1FWbmJuSy1tQjkzck9ITVVhYmVNaEp0NlFvc0JFUTQyWFFlZW1ueU50VlQ1X0szMEt3OXJKQ2lXM1V5a1VCdU9rd3J1REc1aE45RHpJdE9PUlp6cThyckIyRTdIRzVyNDVZdnhBY3FFYjJGaV9ScXFPX05PRmpHR3dEeWl4UWdpdUlJQVlCTUowazU2M3h0RHpKeU5YcEpKUEZIRGw2RFFHVHdjYlNIc1JvNThZMzNFWEVGbThickdtVUHSAfsBQVVfeXFMT3I5WlRtQlN1YXFrYWROT0l4cURXTUhxbXF5VlRZNmRQR2dyUV9BNURhREk2cTBpRHpxb0kzTEg3VHhXc0JLTXdxaWhBc2FzMXU0YzI4NTJ5VTV3MUdTWGxnNS1oVnRzZUk4MXBqQjQ5MHVyMVNvTm5CS3lhMUdRNm5KLUNDZ245eFdfdVBrdndBa0U5eURuQ3B3aXZOSjJCM0hVd1hxVzQ5ejljQmg3SUxmQWR2VllEbTFmamU3SlgyMzJnV3BMa3lhcTZNZlBqU1pSdlk1a25DSDBhNHFhV05KU3AyZmlOTzlVYmhKNW5TOHZCNWVUM3hoUFE?oc=5）</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="180" customHeight="1" s="2">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>印度</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 The Kashmir Horizon报道：Sonam Wangchuk stable, but blood sugar remains low。来源：The Kashmir Horizon（https://news.google.com/rss/articles/CBMilgFBVV95cUxOZ2dfWVNmbnNleU1DZVhNWW1Sb3pZRDRXUEJFNEJOTEVIbkVzWUxXVzZJYzJwQ242SVVJVlRuaFdDdlVkZkpyM0drM3RrSjdpeDR2cVJFMmVGc013Qm9vQXM3Zm01UGI4Z0w1ZDFjUTNmcUQwUnhKQ0Ntb3huQm8zMXAzWUppZnhVaFU2aExreHExd2l5TVE?oc=5）</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="180" customHeight="1" s="2">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>印度</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 ThePrint报道：Wangchuk continues to refuse IV fluids, doctors monitor low blood sugar。来源：ThePrint（https://news.google.com/rss/articles/CBMiqAFBVV95cUxQaTcxZGRTaUtQZUZYN1hJaDQzbWJ0Tl9sR1N5R1N6UUd6NEVsV3ZWV3o4b3cwSk1GVVVkR2ZYS0E0Q0dTZjQtWDJMV1I3NU96Um9VTDdjQkR2el9QRHg0THdBQTdPcjQwT3lWYWZEUmg3ZGRrOXlVMk04cnBzNmpwZmNxZGMyNjl6UUtRS2I0Y24yZ0Jxdm85aUZaV0RnNDVDR3F2WkVxN3fSAa4BQVVfeXFMTkVwNFdvMElENTdybHR4ZjZzN3JuaklwVnRNRVNUTllWbDRDTnl6UkxaRkJubnpKUTQtM3gyVkhOUGZGWkgzc1daUTF6VW5qME4yY2lDUlNrelMtdHNSYmlTYWZVWWViOXZtN1I0SjBKNS1iemFYRzNYdjRhUWpqOXg0bkRmdmQ1RERVQ1o5TmpTajB1Y3I3WnlISDJ5S3RfSnloc3VCdGI2NWI4T3pR?oc=5）</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="180" customHeight="1" s="2">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>印度</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 ChiniMandi报道：Bihar to revive three closed sugar mills, says CM Samrat Choudhary。来源：ChiniMandi（https://news.google.com/rss/articles/CBMimAFBVV95cUxOc1otWG1pQnFjQndOc253YVdGcGxTaXJUWldFa0FxVmFVUlZOLWVvN2ltMHRNMzJhWWN6N2NEd1R5RFpHRkt4MjBicXZ3cjh4dGV2ZUlOaUNXTnBBdjJGc3dUcVd1MXROOUxBdDF2eWQ3QXNmTDU2U2htdzNicVd5c205MUNMY2ZUQ0lxdkp3cXJQT05wN2toTQ?oc=5）</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="180" customHeight="1" s="2">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>印度</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 Capmad报道：Cameroon's sugar imports have almost tripled in five years despite import‑substitution strategy。来源：Capmad（https://news.google.com/rss/articles/CBMivgFBVV95cUxOQUJRTDF0LVhPMkdkMnpkZFVYczJxZ1ZKa08tMDdLSXpCN3UxVXVNTE9Na2dMb3hrZU5jS0FBLVRQWjZGVHEyMDN0TE9UNFV6Qm5qNnNTVl9aTjFEdWpCb1RzZEp2dGhwQmtHZ1V5YUVRc1RsU3Mtcm1jdFVtcGM4akpONjB3Vi01X1dYci1zMXV1TkRZcXNEb0dmcEdwcU5vOVhNYWhEalR2ejBNaVVIa1BnS0txc05vWE9sSGJR?oc=5）</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>偏空糖价：供应或进口增加可能提高市场可用糖源。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="180" customHeight="1" s="2">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>印度</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 PUNE PULSE报道：Sugar Price Hike: Wholesale Rates Climb to ₹4,750 Per Quintal Amid Supply Crunch。来源：PUNE PULSE（https://news.google.com/rss/articles/CBMitgFBVV95cUxOTGNVNWhSQ2NSSzVSTGcxbXFrN2hFRXc2am5Lb2VCdXBPdVlxYS1wOFpsMDVCbndsajFvSzZ0dHF6bnRENjNkXzVFNVNidmFMZEJkQTk0eTk4aXlOZHF1cWN5TTR5dlhaYmpxQy1LRUJhNGNERjZCTk81Y1ZYZXFEMEVjbWx4WGw0bXFDUjZJeFpkdE02TjlkQjFDM19FUUtTUzdadlIxTi1qUDBuQnhfOUJUOVI4dw?oc=5）</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="180" customHeight="1" s="2">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>泰国</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 FBC News报道：Sugar supplies to normalize in coming weeks。来源：FBC News（https://news.google.com/rss/articles/CBMiggFBVV95cUxNLTBia2NSZXFVTGliWUF4NjhFLXZXeHJBUkF6UHhEZldUY3Jud1UzYmJHdE5NemNwMThuRWlRWGRERGVveThLb3ByOTFrQmdGbk42aTVHbzdKZHJiS1JjV2l6bE9FWnhrQXRsdmk5MkZEWVVOQ3VnamFMSEZtd3hmUERB?oc=5）</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="180" customHeight="1" s="2">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>泰国</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 ChiniMandi报道：Uttar Pradhesh: Shamli strengthens position as UP's sugarcane powerhouse under Yogi government。来源：ChiniMandi（https://news.google.com/rss/articles/CBMivAFBVV95cUxQektVS0VtcUlQSnQtbW5hNjljLWF4czNqRkEzb1MzWUhTRndHN25uUTRzX1VuVi1Scm0tWFdyTFJpNFZNRHFyRlp0YlViVzVEdmZVS1kxdHFydVJqcmNBcENDeEpMQ2N2akNBNUF2X2RUSTI2ZjhQcnJpNU4tMWZDMFkzT2k1NjRwVmdqQjZmd2VuWjdpaE9RbngyRmotS1hlY29EN0ZiU1NBQjRRV2JxOEE4Slg0V3doYlJpNA?oc=5）</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="180" customHeight="1" s="2">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>泰国</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 Fiji Sun报道：FSC moves to restore sugar supplies in supermarkets。来源：Fiji Sun（https://news.google.com/rss/articles/CBMijwFBVV95cUxPZGs0cWNWMFFrbjdxVlFvV1Jnc21JOWtZcFFsX01kdGxoWmxMT29vM0NpeHA3bTBPZFB3UHlITTJqOWJYSmk2SUJwRkp3NjlzaklkN1JiTlVodnJlTGdRd2kwU19QQW41bGFoQXUyVUZZSkhNMEdIUnZJU0xZZUM4YnZVS1pReXNQa2F0bzF1Yw?oc=5）</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="180" customHeight="1" s="2">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>欧盟</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 The Hindu报道：Farmers optimistic about TVK government endorsing proposal for modernising Amaravathi Cooperative Sugar Mill。来源：The Hindu（https://news.google.com/rss/articles/CBMijgJBVV95cUxOb3dVdWdqMjVlaFRtaUYtNFFwdmFWcDdrLXYwZlJiUUh0M09DSFRyeW10c2Q0ZDdaa3RNamEzRGUtRWxkNUtVT2JtLTRDVGFRV1lReFE5RTYwWm4tc1lwd2FoNkxQM0t3VlgwRTVLZlJBcW5fb3R2cmttdWNldUZ2QkVQS1NDaVFFLVVtVl9kd2lxVjZBOVRZX20yRlVyQkVVT1N4N2xOQ3dpeThKc1ZiZWJ3Q3h4QkFJYllHR3EwNGwwVnFzcWpiaVpvLVJCWlhpaGVZOGljSUlmbjJ0MGprbE4zZ3ozZnl1WUZsRWlHSC1YbWw5SUJFbl9qR1ZzWnlUVWwxem9jbUtUUWNFNEHSAY4CQVVfeXFMTm93VXVnajI1ZWhUbWlGLTRRcHZhVnA3ay12MGZSYlFIdDNPQ0hUcnltdHNkNGQ3Wmt0TWphM0RlLUVsZDVLVU9ibS00Q1RhUVdZUXhROUU2MFpuLXNZcHdhaDZMUDNLd1ZYMEU1S2ZSQXFuX290dnJrbXVjZXVGdkJFUEtTQ2lRRS1VbVZfZHdpcVY2QTlUWV9tMkZVckJFVU9TeDdsTkN3aXk4SnNWYmVid0N4eEJBSWJZR0dxMDRsMFZxc3FqYmlaby1SQlpYaWhlWThpY0lJZm4ydDBqa2xOM2d6M2Z5dVlGbEVpR0gtWG1sOUlCRW5fakdWc1p5VFVsMXpvY21LVFFjRTRB?oc=5）</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="180" customHeight="1" s="2">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Adecoagro收购巴西南马托格罗索州Caarapó糖醇厂，相关资产具备食糖、含水乙醇、无水乙醇和能源生产能力。交易主要影响巴西糖醇产能归属和企业调配能力，短期不直接改变当期糖产量。来源：ChiniMandi（https://news.google.com/rss/articles/CBMikAFBVV95cUxPZkUtbV9IUkhSUS1YbjgwQXhQbUlNclhhQ0IzU3p1eGZpNm1KMlJFZ2t2RVpJc3MzempTVC0wbHlsTjB4eFkzUjU0aUFrc3QtUURxQmh4ZW0yV2N0RGNvUENCOHpOak9xWUdBLTFtSmtIU3BoN0dCOGlkX3g2V1JGSDcyUWMzci1KSVo5TVRJUE8?oc=5）</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>中性：资产整合提升企业糖醇调配弹性，但交易本身不等于新增供应或即时减产。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1" s="2">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Lokshakti Sugar向SED采购多套制糖设备，目标是提升食糖生产效率和工厂运行水平。该消息反映印度糖厂仍在推进设备更新，但未披露新增压榨量或产糖量。来源：Press Trust of India（https://news.google.com/rss/articles/CBMi1wFBVV95cUxONDRJa1ltOXFoOUtlR2xNSktVTTBLcDRyeHl1ekZxSW9BYUU3RHJtalhXODRnMWZlUU84N2xabGZXVm9JQXgxYU11U0R1QmlSbnZFdkNPbThFbl96TFg0QUlFOUlWUkpuaGxtTl8yMlNOdVFSQk1QRDlENDNiZmpzWDBCZE9QaGtlYU95MmgtejY5OEJJLUVXelpsTEwxcmZNaVFwbTNRcDhJdDN6aHpVM1FwTVgydjZkeUw5M0tROTlkMnFpU2VyZzdkZjkybUd1cEdMVllwMA?oc=5）</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>中性：设备投资有利于中长期生产效率，短期对印度食糖供应和糖价影响有限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1" s="2">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>北方邦政府表示，该邦在印度食糖、甘蔗和乙醇生产中保持领先，是印度最重要的甘蔗和糖业产区之一。该信息强化北方邦在印度糖醇供给中的权重，但未给出新的产量或库存变化。来源：ChiniMandi（https://news.google.com/rss/articles/CBMiogFBVV95cUxPV1FkN0RRWV92Q09yU2dEUUZfSC1PcThidlZuSENFVmVfM2k0YjlyNjYtVW44S0pfM19pdEFXTTBiS1dJcVpsMDZLcWlETlZuTjNVMGFNTElreE1MaVNaandoeGUwNkJ1d2JBbFV0M1ZXc2JOWjlJU3YtNlZsZFdwZ1lVUXVzVmlwcXVkc3JtYjRPeVV6eHZWclllSE9iRmkwWkE?oc=5）</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>中性：产区地位信息有助于判断供给重心，但缺少新增供需数据，短期价格影响有限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1" s="2">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>安得拉邦甘蔗种植受到厄尔尼诺相关天气担忧影响，市场关注后续水分条件和单产表现。若天气不利持续，可能压制当地甘蔗供应，但当前报道未确认实际减产。来源：ChiniMandi（https://news.google.com/rss/articles/CBMinwFBVV95cUxQcGJRWWttWDRyUHJuNDJ5dTRlNkpLZEg2MUFOSDlGczhRY19lWlpWTDZTdWFPcERjdFhmbU5QNEdzQlk4T1ZUUmZTLW5RSjdjeDRVeVV5Wk9ocXI3V1Q3WjBITE90eEN0RlBnOHF5TFQ2SVdNZW0zanBnZ2JuSXc1VzJzYWVOXzd2S2xFUDFMYmdJUXdyNGoyUnNWZURNbVE?oc=5）</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>利多：天气风险可能削弱甘蔗生长和未来糖料供应，但影响仍需后续产区数据验证。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1" s="2">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>卡纳塔克邦Belagavi拟推进13个新糖厂项目，显示当地糖业产能扩张意愿较强。若项目落地，将提高区域甘蔗消化和制糖能力，但短期仍处规划或审批阶段。来源：ChiniMandi（https://news.google.com/rss/articles/CBMiugFBVV95cUxQclpwbzdmeE1MUVJmNXZjUlVRbEtmS0hjeGlJVTZhN3JlZWRRNlVYLTVCamk3MDM1Q2xkQ0o3VlVIdVlBWFFKOHluLTRwdmxDU0RxNl9vdnotMURiTWNkYWxaY2N6VHljS3JDcm1pckp5Y2ZqZS1teXo4YmxySTEzSlU3OXdBbU1FakswUUtDODJJODEtN0tKTjBESnlmaW5ac2JWaWRpUENOMTVuUUdmbWFqeFMzMjY1OUE?oc=5）</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>中性：潜在产能扩张偏向增加未来供应，但项目尚未转化为当期产量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1" s="2">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>印度食糖贸易机构表示，市场对食糖短缺的担忧缺乏依据，并呼吁糖厂和贸易商维持稳定供应。该表态指向库存和供应仍可满足需求，但也说明近期现货供应预期受到市场关注。来源：Siliconindia（https://news.google.com/rss/articles/CBMizgFBVV95cUxNbVFIbmZQTnZwbGdUdHdkck13M1Y2OF9yR0JqU2g5TmJKTXFta3dyX0JSS1NRSmh6dzlSX2FjbExqWFVBZnRlMjRlOXVzaHdjbDhXbFpVYVRrT0hFTXVIMUYzcV8tNXpXYkszUmRqZDFjUGxmZF9WR1VraU5nMW9Vc21Gdy16cWpLaVY1VTlMdlUwcjlOc29BU3MyNlZtMWRFVllBc0JJR0NBTTlQd1JEX1ZoMUczTlFDQW55UEY2YnJxbXhOMUI5dnlPa0pBdw?oc=5）</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>利空：行业强调供应稳定，有助于缓解短缺预期和现货囤货情绪。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1" s="2">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>比哈尔邦表示将重启三家已关闭糖厂，以恢复当地糖业加工能力。若重启顺利，将增加甘蔗压榨和食糖生产能力，但对当期供应影响取决于复产进度。来源：ChiniMandi（https://news.google.com/rss/articles/CBMimAFBVV95cUxOc1otWG1pQnFjQndOc253YVdGcGxTaXJUWldFa0FxVmFVUlZOLWVvN2ltMHRNMzJhWWN6N2NEd1R5RFpHRkt4MjBicXZ3cjh4dGV2ZUlOaUNXTnBBdjJGc3dUcVd1MXROOUxBdDF2eWQ3QXNmTDU2U2htdzNicVd5c205MUNMY2ZUQ0lxdkp3cXJQT05wN2toTQ?oc=5）</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>中性：糖厂复产有利于中期供应恢复，短期产量贡献仍不确定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1" s="2">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>印度现货市场在供应偏紧背景下出现食糖批发价上涨，报道价格达到₹4,750/公担。价格上行反映局部现货供应或采购情绪偏紧，但需要结合主产区报价和库存进一步验证。来源：PUNE PULSE（https://news.google.com/rss/articles/CBMitgFBVV95cUxOTGNVNWhSQ2NSSzVSTGcxbXFrN2hFRXc2am5Lb2VCdXBPdVlxYS1wOFpsMDVCbndsajFvSzZ0dHF6bnRENjNkXzVFNVNidmFMZEJkQTk0eTk4aXlOZHF1cWN5TTR5dlhaYmpxQy1LRUJhNGNERjZCTk81Y1ZYZXFEMEVjbWx4WGw0bXFDUjZJeFpkdE02TjlkQjFDM19FUUtTUzdadlIxTi1qUDBuQnhfOUJUOVI4dw?oc=5）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>利多：现货批发价上涨通常反映短期供应偏紧或需求改善，对糖价形成支撑。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1" s="2">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>印度Amaravathi合作糖厂现代化改造方案获得TVK政府支持，农户对项目推进持乐观态度。该项目关系到当地糖厂加工效率和甘蔗消化能力，但尚未形成新的产量数据。来源：The Hindu（https://news.google.com/rss/articles/CBMijgJBVV95cUxOb3dVdWdqMjVlaFRtaUYtNFFwdmFWcDdrLXYwZlJiUUh0M09DSFRyeW10c2Q0ZDdaa3RNamEzRGUtRWxkNUtVT2JtLTRDVGFRV1lReFE5RTYwWm4tc1lwd2FoNkxQM0t3VlgwRTVLZlJBcW5fb3R2cmttdWNldUZ2QkVQS1NDaVFFLVVtVl9kd2lxVjZBOVRZX20yRlVyQkVVT1N4N2xOQ3dpeThKc1ZiZWJ3Q3h4QkFJYllHR3EwNGwwVnFzcWpiaVpvLVJCWlhpaGVZOGljSUlmbjJ0MGprbE4zZ3ozZnl1WUZsRWlHSC1YbWw5SUJFbl9qR1ZzWnlUVWwxem9jbUtUUWNFNEHSAY4CQVVfeXFMTm93VXVnajI1ZWhUbWlGLTRRcHZhVnA3ay12MGZSYlFIdDNPQ0hUcnltdHNkNGQ3Wmt0TWphM0RlLUVsZDVLVU9ibS00Q1RhUVdZUXhROUU2MFpuLXNZcHdhaDZMUDNLd1ZYMEU1S2ZSQXFuX290dnJrbXVjZXVGdkJFUEtTQ2lRRS1VbVZfZHdpcVY2QTlUWV9tMkZVckJFVU9TeDdsTkN3aXk4SnNWYmVid0N4eEJBSWJZR0dxMDRsMFZxc3FqYmlaby1SQlpYaWhlWThpY0lJZm4ydDBqa2xOM2d6M2Z5dVlGbEVpR0gtWG1sOUlCRW5fakdWc1p5VFVsMXpvY21LVFFjRTRB?oc=5）</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>中性：糖厂现代化有利于中长期加工能力，短期对供需平衡影响有限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1" s="2">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>印度政府表示，公共部门油销公司在三个乙醇供应年度累计乙醇采购支出超过1.72万亿卢比，乙醇采购体系规模继续扩大。若甘蔗汁、糖浆或糖蜜制乙醇需求保持较高水平，将影响甘蔗在制糖和制醇之间的分配。来源：indiagazette.com（https://news.google.com/rss/articles/CBMixgFBVV95cUxQVTFwVEFXeU5zNENTdXVrSGhNZ19sYldQVWY3bmE2X3hsamMxSENNS0E3OE9UMGIteTd5TUdFMFZwS3psbHdFaV9TYzBXOU9wWXlKQ3pVWW95R3Q5Z1VQX0Y4VU5jbkFaZjdVYWJlSU9aTnd1ZDBXc2lvb0pvaDBKNU9ZcHpsVmNzN2FCOHZITHRUNGI1WEtGcmNKREtpOUR3WXhJaUZJMTVLdFU2cV9MSm15VTNTU1FZZnhEZVVEMWlzc1p1QUE?oc=5）</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>利多：乙醇采购规模扩大有利于维持糖蜜和甘蔗制醇需求，可能减少部分食糖供应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1" s="2">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>印度</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>北方邦Shamli在地方政策推动下继续巩固甘蔗主产区地位，反映该地区甘蔗生产和糖厂体系仍受政策支持。该信息偏向产区结构和产业基础，未披露新的产量变化。来源：ChiniMandi（https://news.google.com/rss/articles/CBMivAFBVV95cUxQektVS0VtcUlQSnQtbW5hNjljLWF4czNqRkEzb1MzWUhTRndHN25uUTRzX1VuVi1Scm0tWFdyTFJpNFZNRHFyRlp0YlViVzVEdmZVS1kxdHFydVJqcmNBcENDeEpMQ2N2akNBNUF2X2RUSTI2ZjhQcnJpNU4tMWZDMFkzT2k1NjRwVmdqQjZmd2VuWjdpaE9RbngyRmotS1hlY29EN0ZiU1NBQjRRV2JxOEE4Slg0V3doYlJpNA?oc=5）</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>中性：主产区建设有助于稳定糖料基础，但短期不直接改变食糖供应。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1" s="2">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>印度尼西亚</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 ChiniMandi报道：Indonesia targets E10 ethanol-blended gasoline rollout in 2027, eyes gradual move to E20。来源：ChiniMandi（https://news.google.com/rss/articles/CBMitgFBVV95cUxQYmNnY0R2cTNYV0JWWGwtd0xOallpQi1HQXRDUkZnU2pyZlNfeTZoWHlmZUFOS1drOWhMVVV5ckpaZ2wzMW1XM3VsSzNxX04wbnBIcFRVZmNLYnpzanYzalRnQXJYOXJidmlDdmRWS3VOVTlvRVhQNmJONEtldENOV0dBeEJpMmU1c3JkUFhiOWdCRHFwdm1YdEstaG9lcGI4b3o2dTlVWXQzVW9HZE0tWGtkYk1wdw?oc=5）</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>偏多糖价：乙醇需求或政策推进可能增加糖料制醇吸引力，减少部分制糖供应。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="180" customHeight="1" s="2">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>欧盟</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 FarmingUK报道：British Sugar plans to end Cantley beet processing。来源：FarmingUK（https://news.google.com/rss/articles/CBMilwFBVV95cUxPRzdCQ1R5VEdWbjZ0eno0ZlVIYWZXekMtRk03QW43Y3ZyS1BYeFI2dVR0WDRPY09aN3JmRWhTTjd3b1Z0UzJsNC1BS05zOVJ4TmhIa1h3Njh0VDlvS1B3QUVXUkFEanBRd1FoUHVWRk9hZWpGeGdka2NpeUd4SDBUaG1WQmJ0MXRvYThMNzFDVDMzZHJGZ0lj?oc=5）</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>中性：该信息需要继续跟踪，短期对当期糖产量和出口量的直接影响有限。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="180" customHeight="1" s="2">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>欧盟</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-21 indiagazette.com报道：PSU OMCs spend over Rs 1.72 lakh crore on ethanol procurement across three ESYs: Govt。来源：indiagazette.com（https://news.google.com/rss/articles/CBMixgFBVV95cUxQVTFwVEFXeU5zNENTdXVrSGhNZ19sYldQVWY3bmE2X3hsamMxSENNS0E3OE9UMGIteTd5TUdFMFZwS3psbHdFaV9TYzBXOU9wWXlKQ3pVWW95R3Q5Z1VQX0Y4VU5jbkFaZjdVYWJlSU9aTnd1ZDBXc2lvb0pvaDBKNU9ZcHpsVmNzN2FCOHZITHRUNGI1WEtGcmNKREtpOUR3WXhJaUZJMTVLdFU2cV9MSm15VTNTU1FZZnhEZVVEMWlzc1p1QUE?oc=5）</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>偏多糖价：乙醇需求或政策推进可能增加糖料制醇吸引力，减少部分制糖供应。</t>
-        </is>
-      </c>
-    </row>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>印尼计划2027年推广E10乙醇汽油，并逐步向E20过渡。若乙醇政策与甘蔗、糖蜜或糖业自给政策衔接，可能提升区域制醇原料需求，但当前对国际食糖供需的影响仍偏中长期。来源：BioEnergy Times；ChiniMandi（https://news.google.com/rss/articles/CBMiqwFBVV95cUxPWXJoODE4aVNhaklPblhDTEpyQ2NnX3ZTaFEtZGVnMDNVWDlIcTlMSW5Xc3VDelpIZHUxRmdpaHhWRkh2VDRRa3plQm40Q2xDanc1OUZBczBibXdjTXBHM2VXb0M3WV9wYlN5dGo4UEc0TnBuRTI4cGhWTmlTRXZIMjhaQUJZendmemZrUjd4R215dGpIYzhkamNCbUpnOFBxcnRnRVBFcHJEdWs?oc=5）；ChiniMandi（https://news.google.com/rss/articles/CBMitgFBVV95cUxQYmNnY0R2cTNYV0JWWGwtd0xOallpQi1HQXRDUkZnU2pyZlNfeTZoWHlmZUFOS1drOWhMVVV5ckpaZ2wzMW1XM3VsSzNxX04wbnBIcFRVZmNLYnpzanYzalRnQXJYOXJidmlDdmRWS3VOVTlvRVhQNmJONEtldENOV0dBeEJpMmU1c3JkUFhiOWdCRHFwdm1YdEstaG9lcGI4b3o2dTlVWXQzVW9HZE0tWGtkYk1wdw?oc=5）</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>利多：乙醇掺混目标提高可能增加制醇原料需求，但短期影响取决于原料来源和产能建设进度。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1" s="2">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>斐济</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>斐济相关部门和FSC正推动恢复超市食糖供应，市场预计未来几周供应逐步正常。与此同时，监管部门缺乏超市食糖跟踪系统，说明当地终端供应监测仍存在短板。来源：FBC News；Fiji Sun（https://news.google.com/rss/articles/CBMiggFBVV95cUxNLTBia2NSZXFVTGliWUF4NjhFLXZXeHJBUkF6UHhEZldUY3Jud1UzYmJHdE5NemNwMThuRWlRWGRERGVveThLb3ByOTFrQmdGbk42aTVHbzdKZHJiS1JjV2l6bE9FWnhrQXRsdmk5MkZEWVVOQ3VnamFMSEZtd3hmUERB?oc=5）；FBC News（https://news.google.com/rss/articles/CBMiiAFBVV95cUxQWkVlOE1PYU9RdWtDNVNfcS1jNGxSLXhoUGhmSks5eVkxOEE4TmZJUVA5WG90MXZQZDBySlQyeXhXb0FjcmdHb1F3ZklHVFZxYkFPYXlmZlhKTHdYWU1JZFdOaEpjWm03VmRqTXZRcEMwVjRTZ25LOEZ1SlVGWENjMUVmd2hHVEdi?oc=5）；Fiji Sun（https://news.google.com/rss/articles/CBMijwFBVV95cUxPZGs0cWNWMFFrbjdxVlFvV1Jnc21JOWtZcFFsX01kdGxoWmxMT29vM0NpeHA3bTBPZFB3UHlITTJqOWJYSmk2SUJwRkp3NjlzaklkN1JiTlVodnJlTGdRd2kwU19QQW41bGFoQXUyVUZZSkhNMEdIUnZJU0xZZUM4YnZVS1pReXNQa2F0bzF1Yw?oc=5）</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>中性：该事件主要影响斐济国内零售供应，若恢复顺利，对国际糖价影响有限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1" s="2">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>英国</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>British Sugar计划停止Cantley工厂甜菜加工业务，涉及英国甜菜糖产业的加工布局调整。若产能退出落地，可能改变英国本土甜菜收购和加工安排，但短期供应影响仍取决于替代工厂承接能力。来源：FarmingUK（https://news.google.com/rss/articles/CBMilwFBVV95cUxPRzdCQ1R5VEdWbjZ0eno0ZlVIYWZXekMtRk03QW43Y3ZyS1BYeFI2dVR0WDRPY09aN3JmRWhTTjd3b1Z0UzJsNC1BS05zOVJ4TmhIa1h3Njh0VDlvS1B3QUVXUkFEanBRd1FoUHVWRk9hZWpGeGdka2NpeUd4SDBUaG1WQmJ0MXRvYThMNzFDVDMzZHJGZ0lj?oc=5）</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>中性：单厂加工调整可能影响区域甜菜消化，但目前尚不能确认全国糖供应明显收缩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1" s="2">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>喀麦隆</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>喀麦隆在推进进口替代战略的同时，食糖进口量五年内仍接近增长两倍。进口依赖上升说明国内生产或供应体系仍难完全满足需求，对当地市场供应形成补充。来源：Capmad（https://news.google.com/rss/articles/CBMivgFBVV95cUxOQUJRTDF0LVhPMkdkMnpkZFVYczJxZ1ZKa08tMDdLSXpCN3UxVXVNTE9Na2dMb3hrZU5jS0FBLVRQWjZGVHEyMDN0TE9UNFV6Qm5qNnNTVl9aTjFEdWpCb1RzZEp2dGhwQmtHZ1V5YUVRc1RsU3Mtcm1jdFVtcGM4akpONjB3Vi01X1dYci1zMXV1TkRZcXNEb0dmcEdwcU5vOVhNYWhEalR2ejBNaVVIa1BnS0txc05vWE9sSGJR?oc=5）</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>利空：进口增加提高当地可用糖源，但对国际糖价影响取决于采购规模和来源国。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="180" customHeight="1" s="2"/>
+    <row r="19" ht="180" customHeight="1" s="2"/>
+    <row r="20" ht="180" customHeight="1" s="2"/>
+    <row r="21" ht="180" customHeight="1" s="2"/>
+    <row r="22" ht="180" customHeight="1" s="2"/>
+    <row r="23" ht="180" customHeight="1" s="2"/>
+    <row r="24" ht="180" customHeight="1" s="2"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
